--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JagalchiHang\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7243DE7-A737-48C1-8972-03C9AA24D930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F9E029-F75D-4D80-A3CA-0AB66F787272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3165" yWindow="1635" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>몬스터 이름</t>
   </si>
@@ -43,9 +43,6 @@
     <t>프리팹경로</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -55,9 +52,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>MaxHp</t>
   </si>
   <si>
@@ -95,13 +89,39 @@
   <si>
     <t>monster_3</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이디</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_2</t>
+  </si>
+  <si>
+    <t>Monster_3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -135,6 +155,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -156,11 +183,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -379,150 +407,168 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1">
-        <v>30</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="C6" s="1">
         <v>50</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
         <v>20</v>
-      </c>
-      <c r="D6" s="1">
-        <v>3.5</v>
       </c>
       <c r="E6" s="1">
         <v>3.5</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H9" s="3"/>
+      <c r="F6" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JagalchiHang\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\팀과제\JagalchiHang\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F9E029-F75D-4D80-A3CA-0AB66F787272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DF43FC-AD43-437F-863D-60DDFA8C4C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3165" yWindow="1635" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1272" yWindow="2064" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -70,12 +70,6 @@
     <t>PrefabPath</t>
   </si>
   <si>
-    <t>1번몬스터설명</t>
-  </si>
-  <si>
-    <t>2번몬스터설명</t>
-  </si>
-  <si>
     <t>3번몬스터설명</t>
   </si>
   <si>
@@ -115,13 +109,33 @@
   </si>
   <si>
     <t>Monster_3</t>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번몬스터설명</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -162,6 +176,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -183,12 +204,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -408,20 +430,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -445,12 +467,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -472,12 +494,12 @@
       </c>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -498,12 +520,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1">
         <v>30</v>
@@ -517,16 +539,16 @@
       <c r="F4" s="1">
         <v>1.3</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>16</v>
+      <c r="G4" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <v>40</v>
@@ -540,16 +562,16 @@
       <c r="F5" s="1">
         <v>2.4</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>50</v>
@@ -564,14 +586,15 @@
         <v>3.5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I9" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\팀과제\JagalchiHang\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65DF43FC-AD43-437F-863D-60DDFA8C4C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1620A6-1960-430D-A1D6-5262EDB4CCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1272" yWindow="2064" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>몬스터 이름</t>
   </si>
@@ -70,21 +70,10 @@
     <t>PrefabPath</t>
   </si>
   <si>
-    <t>3번몬스터설명</t>
-  </si>
-  <si>
     <t>monster_1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>monster_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>monster_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -105,30 +94,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Monster_2</t>
-  </si>
-  <si>
-    <t>Monster_3</t>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>번몬스터설명</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>로봇</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Monster</t>
   </si>
 </sst>
 </file>
@@ -443,7 +413,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -469,10 +439,10 @@
     </row>
     <row r="2" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -496,10 +466,10 @@
     </row>
     <row r="3" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -522,10 +492,10 @@
     </row>
     <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1">
         <v>30</v>
@@ -540,54 +510,29 @@
         <v>1.3</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1">
-        <v>40</v>
-      </c>
-      <c r="D5" s="1">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I9" s="3"/>

--- a/JsonConverter/ExcelFiles/MonsterData.xlsx
+++ b/JsonConverter/ExcelFiles/MonsterData.xlsx
@@ -21,73 +21,73 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
     <x:t>로봇</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
     <x:t>BasicAttackRange</x:t>
   </x:si>
   <x:si>
     <x:t>MonsterDescription</x:t>
   </x:si>
   <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프리팹경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본공격사거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본이동속도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>monster_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Monster_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BasicAttack</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BasicSpeed</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefab/Monster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BasicSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>monster_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Monster_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본공격사거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본이동속도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프리팹경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BasicAttack</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -164,22 +164,22 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -800,92 +800,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="13.199999999999999">
       <x:c r="A1" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:8" ht="13.199999999999999">
       <x:c r="A3" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8" ht="13.199999999999999">
       <x:c r="A4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="2">
-        <x:v>30</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D4" s="2">
         <x:v>8</x:v>
@@ -897,10 +897,10 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="G4" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7" ht="13.199999999999999">
@@ -925,7 +925,7 @@
       <x:c r="I9" s="4"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>